--- a/artfynd/A 9688-2023 artfynd.xlsx
+++ b/artfynd/A 9688-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 9688-2023 artfynd.xlsx
+++ b/artfynd/A 9688-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113458967</v>
+        <v>113380629</v>
       </c>
       <c r="B2" t="n">
-        <v>104650</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106156</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
